--- a/physical_location_labelling/physical_location_by_context/v06_case_pairs/casepairs.xlsx
+++ b/physical_location_labelling/physical_location_by_context/v06_case_pairs/casepairs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eestikeeleinstituut-my.sharepoint.com/personal/kertu_saul_eki_ee/Documents/Dokumendid/doktoritoo/estnltk_syntax_repo_kloon/physical_location_labelling/physical_location_by_context/v06_case_pairs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4822" documentId="8_{37F4B448-035C-43B4-8DEF-42C28217B0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41C5CFD2-D723-4EF4-AF04-C7147FF1B716}"/>
+  <xr:revisionPtr revIDLastSave="4941" documentId="8_{37F4B448-035C-43B4-8DEF-42C28217B0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03E39408-E8F3-4CFD-BC27-92DE17EB7CBD}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{6F54A803-3B66-4EA4-BE44-316809BC0A03}"/>
   </bookViews>
@@ -8655,7 +8655,14 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F2074B5A-6FAD-40A7-950E-6A8BB34DC3DE}" name="transaction_case_pair_examples" displayName="transaction_case_pair_examples" ref="A1:S841" tableType="queryTable" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
-  <autoFilter ref="A1:S841" xr:uid="{F2074B5A-6FAD-40A7-950E-6A8BB34DC3DE}"/>
+  <autoFilter ref="A1:S841" xr:uid="{F2074B5A-6FAD-40A7-950E-6A8BB34DC3DE}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="el"/>
+        <filter val="ill"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{2126D6EA-41FB-426B-AD41-2266DCF9921A}" uniqueName="1" name="case_pair" queryTableFieldId="1" dataDxfId="40"/>
     <tableColumn id="2" xr3:uid="{59A023B8-16B2-491E-88B1-FAB34F714CEA}" uniqueName="2" name="sentence_id" queryTableFieldId="2" dataDxfId="39"/>
@@ -9119,7 +9126,7 @@
         <v>2768</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -9172,7 +9179,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -9216,7 +9223,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -9260,7 +9267,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -9313,7 +9320,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -9360,7 +9367,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -9404,7 +9411,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -9460,7 +9467,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -9513,7 +9520,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="189.45" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" ht="189.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -9569,7 +9576,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -9616,7 +9623,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -9663,7 +9670,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -9719,7 +9726,7 @@
         <v>2745</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -9772,7 +9779,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -9825,7 +9832,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
@@ -9878,7 +9885,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
@@ -9922,7 +9929,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>9</v>
       </c>
@@ -9969,7 +9976,7 @@
         <v>2746</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
@@ -10016,13 +10023,13 @@
         <v>2737</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>2750</v>
+        <v>2729</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>2747</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
@@ -10066,7 +10073,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
@@ -11499,7 +11506,7 @@
         <v>2737</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>2750</v>
+        <v>2734</v>
       </c>
       <c r="R48" s="1" t="s">
         <v>2747</v>
@@ -12161,7 +12168,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
         <v>12</v>
       </c>
@@ -12214,7 +12221,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
         <v>12</v>
       </c>
@@ -12258,7 +12265,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
         <v>12</v>
       </c>
@@ -12311,7 +12318,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>12</v>
       </c>
@@ -12367,7 +12374,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
         <v>12</v>
       </c>
@@ -12420,7 +12427,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>12</v>
       </c>
@@ -12464,7 +12471,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
         <v>12</v>
       </c>
@@ -12517,7 +12524,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
         <v>12</v>
       </c>
@@ -12570,7 +12577,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
         <v>12</v>
       </c>
@@ -12623,7 +12630,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
         <v>12</v>
       </c>
@@ -12667,7 +12674,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
         <v>12</v>
       </c>
@@ -12720,7 +12727,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
         <v>12</v>
       </c>
@@ -12773,7 +12780,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A74" s="1" t="s">
         <v>12</v>
       </c>
@@ -12826,7 +12833,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
         <v>12</v>
       </c>
@@ -12879,7 +12886,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
         <v>12</v>
       </c>
@@ -12932,7 +12939,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:19" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A77" s="1" t="s">
         <v>12</v>
       </c>
@@ -12985,7 +12992,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A78" s="1" t="s">
         <v>12</v>
       </c>
@@ -13038,7 +13045,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A79" s="1" t="s">
         <v>12</v>
       </c>
@@ -13091,7 +13098,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A80" s="1" t="s">
         <v>12</v>
       </c>
@@ -13144,7 +13151,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A81" s="1" t="s">
         <v>12</v>
       </c>
@@ -13197,7 +13204,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A82" s="1" t="s">
         <v>13</v>
       </c>
@@ -13250,7 +13257,7 @@
         <v>2747</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A83" s="1" t="s">
         <v>13</v>
       </c>
@@ -13303,7 +13310,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A84" s="1" t="s">
         <v>13</v>
       </c>
@@ -13359,7 +13366,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A85" s="1" t="s">
         <v>13</v>
       </c>
@@ -13412,7 +13419,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="145.75" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:19" ht="145.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A86" s="1" t="s">
         <v>13</v>
       </c>
@@ -13465,7 +13472,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="87" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A87" s="1" t="s">
         <v>13</v>
       </c>
@@ -13518,7 +13525,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A88" s="1" t="s">
         <v>13</v>
       </c>
@@ -13571,7 +13578,7 @@
         <v>2747</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A89" s="1" t="s">
         <v>13</v>
       </c>
@@ -13624,7 +13631,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A90" s="1" t="s">
         <v>13</v>
       </c>
@@ -13677,7 +13684,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A91" s="1" t="s">
         <v>13</v>
       </c>
@@ -13730,7 +13737,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A92" s="1" t="s">
         <v>13</v>
       </c>
@@ -13783,7 +13790,7 @@
         <v>2747</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A93" s="1" t="s">
         <v>13</v>
       </c>
@@ -13836,7 +13843,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A94" s="1" t="s">
         <v>13</v>
       </c>
@@ -13889,7 +13896,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="95" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A95" s="1" t="s">
         <v>13</v>
       </c>
@@ -13942,7 +13949,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="96" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A96" s="1" t="s">
         <v>13</v>
       </c>
@@ -13995,7 +14002,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="97" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A97" s="1" t="s">
         <v>13</v>
       </c>
@@ -14051,7 +14058,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A98" s="1" t="s">
         <v>13</v>
       </c>
@@ -14107,7 +14114,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="160.30000000000001" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:19" ht="160.30000000000001" hidden="1" x14ac:dyDescent="0.4">
       <c r="A99" s="1" t="s">
         <v>13</v>
       </c>
@@ -14163,7 +14170,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A100" s="1" t="s">
         <v>13</v>
       </c>
@@ -14216,7 +14223,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A101" s="1" t="s">
         <v>13</v>
       </c>
@@ -14269,7 +14276,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A102" s="1" t="s">
         <v>14</v>
       </c>
@@ -14322,7 +14329,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A103" s="1" t="s">
         <v>14</v>
       </c>
@@ -14375,7 +14382,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A104" s="1" t="s">
         <v>14</v>
       </c>
@@ -14431,7 +14438,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A105" s="1" t="s">
         <v>14</v>
       </c>
@@ -14484,7 +14491,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A106" s="1" t="s">
         <v>14</v>
       </c>
@@ -14537,7 +14544,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="107" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A107" s="1" t="s">
         <v>14</v>
       </c>
@@ -14590,7 +14597,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
         <v>14</v>
       </c>
@@ -14643,7 +14650,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="109" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A109" s="1" t="s">
         <v>14</v>
       </c>
@@ -14696,7 +14703,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="110" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A110" s="1" t="s">
         <v>14</v>
       </c>
@@ -14749,7 +14756,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="111" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A111" s="1" t="s">
         <v>14</v>
       </c>
@@ -14802,7 +14809,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="112" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A112" s="1" t="s">
         <v>14</v>
       </c>
@@ -14855,7 +14862,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A113" s="1" t="s">
         <v>14</v>
       </c>
@@ -14899,7 +14906,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A114" s="1" t="s">
         <v>14</v>
       </c>
@@ -14952,7 +14959,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A115" s="1" t="s">
         <v>14</v>
       </c>
@@ -15005,7 +15012,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A116" s="1" t="s">
         <v>14</v>
       </c>
@@ -15058,7 +15065,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A117" s="1" t="s">
         <v>14</v>
       </c>
@@ -15111,7 +15118,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A118" s="1" t="s">
         <v>14</v>
       </c>
@@ -15164,7 +15171,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A119" s="1" t="s">
         <v>14</v>
       </c>
@@ -15217,7 +15224,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A120" s="1" t="s">
         <v>14</v>
       </c>
@@ -15270,7 +15277,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A121" s="1" t="s">
         <v>14</v>
       </c>
@@ -15314,7 +15321,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A122" s="1" t="s">
         <v>15</v>
       </c>
@@ -15358,7 +15365,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A123" s="1" t="s">
         <v>15</v>
       </c>
@@ -15402,7 +15409,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A124" s="1" t="s">
         <v>15</v>
       </c>
@@ -15455,7 +15462,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A125" s="1" t="s">
         <v>15</v>
       </c>
@@ -15499,7 +15506,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A126" s="1" t="s">
         <v>15</v>
       </c>
@@ -15543,7 +15550,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A127" s="1" t="s">
         <v>15</v>
       </c>
@@ -15587,7 +15594,7 @@
         <v>2734</v>
       </c>
       <c r="P127" s="1" t="s">
-        <v>2747</v>
+        <v>2737</v>
       </c>
       <c r="Q127" s="1" t="s">
         <v>2728</v>
@@ -15596,7 +15603,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A128" s="1" t="s">
         <v>15</v>
       </c>
@@ -15640,7 +15647,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A129" s="1" t="s">
         <v>15</v>
       </c>
@@ -15693,7 +15700,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A130" s="1" t="s">
         <v>15</v>
       </c>
@@ -15746,7 +15753,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A131" s="1" t="s">
         <v>15</v>
       </c>
@@ -15790,7 +15797,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A132" s="1" t="s">
         <v>15</v>
       </c>
@@ -15843,7 +15850,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A133" s="1" t="s">
         <v>15</v>
       </c>
@@ -15896,7 +15903,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A134" s="1" t="s">
         <v>15</v>
       </c>
@@ -15940,7 +15947,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A135" s="1" t="s">
         <v>15</v>
       </c>
@@ -15993,7 +16000,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A136" s="1" t="s">
         <v>15</v>
       </c>
@@ -16037,7 +16044,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A137" s="1" t="s">
         <v>15</v>
       </c>
@@ -16081,7 +16088,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A138" s="1" t="s">
         <v>15</v>
       </c>
@@ -16125,7 +16132,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A139" s="1" t="s">
         <v>15</v>
       </c>
@@ -16169,7 +16176,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A140" s="1" t="s">
         <v>15</v>
       </c>
@@ -16222,7 +16229,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A141" s="1" t="s">
         <v>15</v>
       </c>
@@ -18221,7 +18228,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A182" s="1" t="s">
         <v>18</v>
       </c>
@@ -18265,7 +18272,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A183" s="1" t="s">
         <v>18</v>
       </c>
@@ -18309,7 +18316,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A184" s="1" t="s">
         <v>18</v>
       </c>
@@ -18353,7 +18360,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A185" s="1" t="s">
         <v>18</v>
       </c>
@@ -18397,7 +18404,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A186" s="1" t="s">
         <v>18</v>
       </c>
@@ -18450,7 +18457,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A187" s="1" t="s">
         <v>18</v>
       </c>
@@ -18494,7 +18501,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A188" s="1" t="s">
         <v>18</v>
       </c>
@@ -18538,7 +18545,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A189" s="1" t="s">
         <v>18</v>
       </c>
@@ -18582,7 +18589,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A190" s="1" t="s">
         <v>18</v>
       </c>
@@ -18626,7 +18633,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A191" s="1" t="s">
         <v>18</v>
       </c>
@@ -18670,7 +18677,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A192" s="1" t="s">
         <v>18</v>
       </c>
@@ -18714,7 +18721,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A193" s="1" t="s">
         <v>18</v>
       </c>
@@ -18758,7 +18765,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A194" s="1" t="s">
         <v>18</v>
       </c>
@@ -18802,7 +18809,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A195" s="1" t="s">
         <v>18</v>
       </c>
@@ -18846,7 +18853,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A196" s="1" t="s">
         <v>18</v>
       </c>
@@ -18890,7 +18897,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A197" s="1" t="s">
         <v>18</v>
       </c>
@@ -18943,7 +18950,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A198" s="1" t="s">
         <v>18</v>
       </c>
@@ -18996,7 +19003,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:18" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A199" s="1" t="s">
         <v>18</v>
       </c>
@@ -19040,7 +19047,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A200" s="1" t="s">
         <v>18</v>
       </c>
@@ -19084,7 +19091,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A201" s="1" t="s">
         <v>18</v>
       </c>
@@ -19128,7 +19135,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A202" s="1" t="s">
         <v>19</v>
       </c>
@@ -19181,7 +19188,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A203" s="1" t="s">
         <v>19</v>
       </c>
@@ -19234,7 +19241,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A204" s="1" t="s">
         <v>19</v>
       </c>
@@ -19287,7 +19294,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A205" s="1" t="s">
         <v>19</v>
       </c>
@@ -19340,7 +19347,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A206" s="1" t="s">
         <v>19</v>
       </c>
@@ -19393,7 +19400,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A207" s="1" t="s">
         <v>19</v>
       </c>
@@ -19437,7 +19444,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A208" s="1" t="s">
         <v>19</v>
       </c>
@@ -19490,7 +19497,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="209" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A209" s="1" t="s">
         <v>19</v>
       </c>
@@ -19543,7 +19550,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="210" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A210" s="1" t="s">
         <v>19</v>
       </c>
@@ -19596,7 +19603,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="211" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A211" s="1" t="s">
         <v>19</v>
       </c>
@@ -19649,7 +19656,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="212" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A212" s="1" t="s">
         <v>19</v>
       </c>
@@ -19702,7 +19709,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="213" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A213" s="1" t="s">
         <v>19</v>
       </c>
@@ -19755,7 +19762,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="214" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -19808,7 +19815,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="215" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A215" s="1" t="s">
         <v>19</v>
       </c>
@@ -19852,7 +19859,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="216" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A216" s="1" t="s">
         <v>19</v>
       </c>
@@ -19893,7 +19900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A217" s="1" t="s">
         <v>19</v>
       </c>
@@ -19946,7 +19953,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="218" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A218" s="1" t="s">
         <v>19</v>
       </c>
@@ -19999,7 +20006,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="219" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A219" s="1" t="s">
         <v>19</v>
       </c>
@@ -20052,7 +20059,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="220" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A220" s="1" t="s">
         <v>19</v>
       </c>
@@ -20108,7 +20115,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="221" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A221" s="1" t="s">
         <v>19</v>
       </c>
@@ -20164,7 +20171,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="222" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A222" s="1" t="s">
         <v>20</v>
       </c>
@@ -20217,7 +20224,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="223" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A223" s="1" t="s">
         <v>20</v>
       </c>
@@ -20261,7 +20268,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="224" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A224" s="1" t="s">
         <v>20</v>
       </c>
@@ -20314,7 +20321,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A225" s="1" t="s">
         <v>20</v>
       </c>
@@ -20358,7 +20365,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A226" s="1" t="s">
         <v>20</v>
       </c>
@@ -20402,7 +20409,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A227" s="1" t="s">
         <v>20</v>
       </c>
@@ -20446,7 +20453,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A228" s="1" t="s">
         <v>20</v>
       </c>
@@ -20499,7 +20506,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A229" s="1" t="s">
         <v>20</v>
       </c>
@@ -20543,7 +20550,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A230" s="1" t="s">
         <v>20</v>
       </c>
@@ -20596,7 +20603,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A231" s="1" t="s">
         <v>20</v>
       </c>
@@ -20640,7 +20647,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A232" s="1" t="s">
         <v>20</v>
       </c>
@@ -20693,7 +20700,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A233" s="1" t="s">
         <v>20</v>
       </c>
@@ -20746,7 +20753,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A234" s="1" t="s">
         <v>20</v>
       </c>
@@ -20799,7 +20806,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A235" s="1" t="s">
         <v>20</v>
       </c>
@@ -20852,7 +20859,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A236" s="1" t="s">
         <v>20</v>
       </c>
@@ -20896,7 +20903,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A237" s="1" t="s">
         <v>20</v>
       </c>
@@ -20940,7 +20947,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A238" s="1" t="s">
         <v>20</v>
       </c>
@@ -20993,7 +21000,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A239" s="1" t="s">
         <v>20</v>
       </c>
@@ -21046,7 +21053,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A240" s="1" t="s">
         <v>20</v>
       </c>
@@ -21099,7 +21106,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="241" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A241" s="1" t="s">
         <v>20</v>
       </c>
@@ -21143,7 +21150,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="242" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A242" s="1" t="s">
         <v>21</v>
       </c>
@@ -21190,7 +21197,7 @@
         <v>2759</v>
       </c>
     </row>
-    <row r="243" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A243" s="1" t="s">
         <v>21</v>
       </c>
@@ -21243,7 +21250,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="244" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A244" s="1" t="s">
         <v>21</v>
       </c>
@@ -21296,7 +21303,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="245" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A245" s="1" t="s">
         <v>21</v>
       </c>
@@ -21349,7 +21356,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="246" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A246" s="1" t="s">
         <v>21</v>
       </c>
@@ -21402,7 +21409,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="247" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A247" s="1" t="s">
         <v>21</v>
       </c>
@@ -21446,7 +21453,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="248" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A248" s="1" t="s">
         <v>21</v>
       </c>
@@ -21499,7 +21506,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="249" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A249" s="1" t="s">
         <v>21</v>
       </c>
@@ -21543,7 +21550,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="250" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A250" s="1" t="s">
         <v>21</v>
       </c>
@@ -21596,7 +21603,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="251" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A251" s="1" t="s">
         <v>21</v>
       </c>
@@ -21649,7 +21656,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="252" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A252" s="1" t="s">
         <v>21</v>
       </c>
@@ -21702,7 +21709,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="253" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A253" s="1" t="s">
         <v>21</v>
       </c>
@@ -21746,7 +21753,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="254" spans="1:19" ht="160.30000000000001" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:19" ht="160.30000000000001" hidden="1" x14ac:dyDescent="0.4">
       <c r="A254" s="1" t="s">
         <v>21</v>
       </c>
@@ -21790,7 +21797,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="255" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A255" s="1" t="s">
         <v>21</v>
       </c>
@@ -21834,7 +21841,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="256" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A256" s="1" t="s">
         <v>21</v>
       </c>
@@ -21887,7 +21894,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="257" spans="1:19" ht="145.75" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:19" ht="145.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A257" s="1" t="s">
         <v>21</v>
       </c>
@@ -21940,7 +21947,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="258" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A258" s="1" t="s">
         <v>21</v>
       </c>
@@ -21993,7 +22000,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="259" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A259" s="1" t="s">
         <v>21</v>
       </c>
@@ -22046,7 +22053,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="260" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A260" s="1" t="s">
         <v>21</v>
       </c>
@@ -22099,7 +22106,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="261" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A261" s="1" t="s">
         <v>21</v>
       </c>
@@ -22152,7 +22159,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="262" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A262" s="1" t="s">
         <v>22</v>
       </c>
@@ -22196,7 +22203,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="263" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A263" s="1" t="s">
         <v>22</v>
       </c>
@@ -22240,7 +22247,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="264" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A264" s="1" t="s">
         <v>22</v>
       </c>
@@ -22284,7 +22291,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="265" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A265" s="1" t="s">
         <v>22</v>
       </c>
@@ -22331,7 +22338,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="266" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A266" s="1" t="s">
         <v>22</v>
       </c>
@@ -22375,7 +22382,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="267" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A267" s="1" t="s">
         <v>22</v>
       </c>
@@ -22422,7 +22429,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="268" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A268" s="1" t="s">
         <v>22</v>
       </c>
@@ -22469,7 +22476,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="269" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A269" s="1" t="s">
         <v>22</v>
       </c>
@@ -22513,7 +22520,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="270" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A270" s="1" t="s">
         <v>22</v>
       </c>
@@ -22557,7 +22564,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="271" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A271" s="1" t="s">
         <v>22</v>
       </c>
@@ -22601,7 +22608,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="272" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A272" s="1" t="s">
         <v>22</v>
       </c>
@@ -22645,7 +22652,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="273" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A273" s="1" t="s">
         <v>22</v>
       </c>
@@ -22689,7 +22696,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="274" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A274" s="1" t="s">
         <v>22</v>
       </c>
@@ -22733,7 +22740,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="275" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A275" s="1" t="s">
         <v>22</v>
       </c>
@@ -22777,7 +22784,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="276" spans="1:19" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:19" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A276" s="1" t="s">
         <v>22</v>
       </c>
@@ -22824,7 +22831,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="277" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A277" s="1" t="s">
         <v>22</v>
       </c>
@@ -22868,7 +22875,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="278" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A278" s="1" t="s">
         <v>22</v>
       </c>
@@ -22912,7 +22919,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="279" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A279" s="1" t="s">
         <v>22</v>
       </c>
@@ -22956,7 +22963,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="280" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A280" s="1" t="s">
         <v>22</v>
       </c>
@@ -23009,7 +23016,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="281" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A281" s="1" t="s">
         <v>22</v>
       </c>
@@ -24035,7 +24042,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A302" s="1" t="s">
         <v>24</v>
       </c>
@@ -24088,7 +24095,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A303" s="1" t="s">
         <v>24</v>
       </c>
@@ -24141,7 +24148,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A304" s="1" t="s">
         <v>24</v>
       </c>
@@ -24194,7 +24201,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="305" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A305" s="1" t="s">
         <v>24</v>
       </c>
@@ -24247,7 +24254,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="306" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A306" s="1" t="s">
         <v>24</v>
       </c>
@@ -24291,7 +24298,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="307" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A307" s="1" t="s">
         <v>24</v>
       </c>
@@ -24344,7 +24351,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="308" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A308" s="1" t="s">
         <v>24</v>
       </c>
@@ -24397,7 +24404,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="309" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A309" s="1" t="s">
         <v>24</v>
       </c>
@@ -24450,7 +24457,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="310" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A310" s="1" t="s">
         <v>24</v>
       </c>
@@ -24494,7 +24501,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="311" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A311" s="1" t="s">
         <v>24</v>
       </c>
@@ -24538,7 +24545,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="312" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A312" s="1" t="s">
         <v>24</v>
       </c>
@@ -24591,7 +24598,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="313" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A313" s="1" t="s">
         <v>24</v>
       </c>
@@ -24635,7 +24642,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="314" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A314" s="1" t="s">
         <v>24</v>
       </c>
@@ -24688,7 +24695,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="315" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A315" s="1" t="s">
         <v>24</v>
       </c>
@@ -24735,7 +24742,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="316" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A316" s="1" t="s">
         <v>24</v>
       </c>
@@ -24788,7 +24795,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="317" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A317" s="1" t="s">
         <v>24</v>
       </c>
@@ -24841,7 +24848,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="318" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A318" s="1" t="s">
         <v>24</v>
       </c>
@@ -24885,7 +24892,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="319" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A319" s="1" t="s">
         <v>24</v>
       </c>
@@ -24938,7 +24945,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="320" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A320" s="1" t="s">
         <v>24</v>
       </c>
@@ -24991,7 +24998,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A321" s="1" t="s">
         <v>24</v>
       </c>
@@ -25035,7 +25042,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A322" s="1" t="s">
         <v>25</v>
       </c>
@@ -25079,7 +25086,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A323" s="1" t="s">
         <v>25</v>
       </c>
@@ -25132,7 +25139,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="324" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A324" s="1" t="s">
         <v>25</v>
       </c>
@@ -25185,7 +25192,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="325" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A325" s="1" t="s">
         <v>25</v>
       </c>
@@ -25238,7 +25245,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="326" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A326" s="1" t="s">
         <v>25</v>
       </c>
@@ -25291,7 +25298,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="327" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A327" s="1" t="s">
         <v>25</v>
       </c>
@@ -25344,7 +25351,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="328" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A328" s="1" t="s">
         <v>25</v>
       </c>
@@ -25397,7 +25404,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="329" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A329" s="1" t="s">
         <v>25</v>
       </c>
@@ -25450,7 +25457,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="330" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A330" s="1" t="s">
         <v>25</v>
       </c>
@@ -25494,7 +25501,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="331" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A331" s="1" t="s">
         <v>25</v>
       </c>
@@ -25547,7 +25554,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="332" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A332" s="1" t="s">
         <v>25</v>
       </c>
@@ -25600,7 +25607,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="333" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A333" s="1" t="s">
         <v>25</v>
       </c>
@@ -25653,7 +25660,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="334" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A334" s="1" t="s">
         <v>25</v>
       </c>
@@ -25706,7 +25713,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A335" s="1" t="s">
         <v>25</v>
       </c>
@@ -25759,7 +25766,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="336" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A336" s="1" t="s">
         <v>25</v>
       </c>
@@ -25812,7 +25819,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="337" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A337" s="1" t="s">
         <v>25</v>
       </c>
@@ -25865,7 +25872,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="338" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A338" s="1" t="s">
         <v>25</v>
       </c>
@@ -25918,7 +25925,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="339" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A339" s="1" t="s">
         <v>25</v>
       </c>
@@ -25971,7 +25978,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="340" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A340" s="1" t="s">
         <v>25</v>
       </c>
@@ -26024,7 +26031,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="341" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A341" s="1" t="s">
         <v>25</v>
       </c>
@@ -26077,7 +26084,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="342" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A342" s="1" t="s">
         <v>26</v>
       </c>
@@ -26130,7 +26137,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="343" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A343" s="1" t="s">
         <v>26</v>
       </c>
@@ -26183,7 +26190,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="344" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A344" s="1" t="s">
         <v>26</v>
       </c>
@@ -26227,7 +26234,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="345" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A345" s="1" t="s">
         <v>26</v>
       </c>
@@ -26280,7 +26287,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="346" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A346" s="1" t="s">
         <v>26</v>
       </c>
@@ -26333,7 +26340,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="347" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A347" s="1" t="s">
         <v>26</v>
       </c>
@@ -26386,7 +26393,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="348" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A348" s="1" t="s">
         <v>26</v>
       </c>
@@ -26439,7 +26446,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="349" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A349" s="1" t="s">
         <v>26</v>
       </c>
@@ -26492,7 +26499,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="350" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A350" s="1" t="s">
         <v>26</v>
       </c>
@@ -26536,7 +26543,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="351" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A351" s="1" t="s">
         <v>26</v>
       </c>
@@ -26580,7 +26587,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="352" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A352" s="1" t="s">
         <v>26</v>
       </c>
@@ -26624,7 +26631,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="353" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A353" s="1" t="s">
         <v>26</v>
       </c>
@@ -26677,7 +26684,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="354" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A354" s="1" t="s">
         <v>26</v>
       </c>
@@ -26721,7 +26728,7 @@
         <v>2754</v>
       </c>
     </row>
-    <row r="355" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A355" s="1" t="s">
         <v>26</v>
       </c>
@@ -26774,7 +26781,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="356" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A356" s="1" t="s">
         <v>26</v>
       </c>
@@ -26827,7 +26834,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="357" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A357" s="1" t="s">
         <v>26</v>
       </c>
@@ -26880,7 +26887,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="358" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A358" s="1" t="s">
         <v>26</v>
       </c>
@@ -26933,7 +26940,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="359" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A359" s="1" t="s">
         <v>26</v>
       </c>
@@ -26986,7 +26993,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="360" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A360" s="1" t="s">
         <v>26</v>
       </c>
@@ -27030,7 +27037,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="361" spans="1:18" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:18" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A361" s="1" t="s">
         <v>26</v>
       </c>
@@ -27074,7 +27081,7 @@
         <v>2734</v>
       </c>
       <c r="P361" s="1" t="s">
-        <v>2747</v>
+        <v>2737</v>
       </c>
       <c r="Q361" s="1" t="s">
         <v>2733</v>
@@ -27083,7 +27090,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="362" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A362" s="1" t="s">
         <v>27</v>
       </c>
@@ -27127,7 +27134,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="363" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A363" s="1" t="s">
         <v>27</v>
       </c>
@@ -27171,7 +27178,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="364" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A364" s="1" t="s">
         <v>27</v>
       </c>
@@ -27224,7 +27231,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="365" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A365" s="1" t="s">
         <v>27</v>
       </c>
@@ -27277,7 +27284,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="366" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A366" s="1" t="s">
         <v>27</v>
       </c>
@@ -27321,7 +27328,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="367" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A367" s="1" t="s">
         <v>27</v>
       </c>
@@ -27374,7 +27381,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="368" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A368" s="1" t="s">
         <v>27</v>
       </c>
@@ -27427,7 +27434,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="369" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A369" s="1" t="s">
         <v>27</v>
       </c>
@@ -27480,7 +27487,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="370" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A370" s="1" t="s">
         <v>27</v>
       </c>
@@ -27533,7 +27540,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="371" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A371" s="1" t="s">
         <v>27</v>
       </c>
@@ -27586,7 +27593,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="372" spans="1:18" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:18" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A372" s="1" t="s">
         <v>27</v>
       </c>
@@ -27639,7 +27646,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="373" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A373" s="1" t="s">
         <v>27</v>
       </c>
@@ -27692,7 +27699,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="374" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A374" s="1" t="s">
         <v>27</v>
       </c>
@@ -27745,7 +27752,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="375" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A375" s="1" t="s">
         <v>27</v>
       </c>
@@ -27789,7 +27796,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="376" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A376" s="1" t="s">
         <v>27</v>
       </c>
@@ -27842,7 +27849,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="377" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A377" s="1" t="s">
         <v>27</v>
       </c>
@@ -27895,7 +27902,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="378" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A378" s="1" t="s">
         <v>27</v>
       </c>
@@ -27948,7 +27955,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="379" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A379" s="1" t="s">
         <v>27</v>
       </c>
@@ -28001,7 +28008,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="380" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A380" s="1" t="s">
         <v>27</v>
       </c>
@@ -28054,7 +28061,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="381" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A381" s="1" t="s">
         <v>27</v>
       </c>
@@ -28107,7 +28114,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="382" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A382" s="1" t="s">
         <v>28</v>
       </c>
@@ -28160,7 +28167,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="383" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A383" s="1" t="s">
         <v>28</v>
       </c>
@@ -28213,7 +28220,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="384" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A384" s="1" t="s">
         <v>28</v>
       </c>
@@ -28257,7 +28264,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="385" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A385" s="1" t="s">
         <v>28</v>
       </c>
@@ -28310,7 +28317,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="386" spans="1:18" ht="160.30000000000001" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:18" ht="160.30000000000001" hidden="1" x14ac:dyDescent="0.4">
       <c r="A386" s="1" t="s">
         <v>28</v>
       </c>
@@ -28363,7 +28370,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="387" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A387" s="1" t="s">
         <v>28</v>
       </c>
@@ -28416,7 +28423,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="388" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A388" s="1" t="s">
         <v>28</v>
       </c>
@@ -28460,7 +28467,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="389" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A389" s="1" t="s">
         <v>28</v>
       </c>
@@ -28513,7 +28520,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="390" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A390" s="1" t="s">
         <v>28</v>
       </c>
@@ -28566,7 +28573,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="391" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A391" s="1" t="s">
         <v>28</v>
       </c>
@@ -28610,7 +28617,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="392" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A392" s="1" t="s">
         <v>28</v>
       </c>
@@ -28654,7 +28661,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="393" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A393" s="1" t="s">
         <v>28</v>
       </c>
@@ -28707,7 +28714,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="394" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A394" s="1" t="s">
         <v>28</v>
       </c>
@@ -28760,7 +28767,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="395" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A395" s="1" t="s">
         <v>28</v>
       </c>
@@ -28813,7 +28820,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="396" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A396" s="1" t="s">
         <v>28</v>
       </c>
@@ -28866,7 +28873,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="397" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A397" s="1" t="s">
         <v>28</v>
       </c>
@@ -28919,7 +28926,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="398" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A398" s="1" t="s">
         <v>28</v>
       </c>
@@ -28972,7 +28979,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="399" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A399" s="1" t="s">
         <v>28</v>
       </c>
@@ -29025,7 +29032,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="400" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A400" s="1" t="s">
         <v>28</v>
       </c>
@@ -29078,7 +29085,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="401" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A401" s="1" t="s">
         <v>28</v>
       </c>
@@ -30191,7 +30198,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="422" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A422" s="1" t="s">
         <v>30</v>
       </c>
@@ -30244,7 +30251,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="423" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A423" s="1" t="s">
         <v>30</v>
       </c>
@@ -30288,7 +30295,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="424" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A424" s="1" t="s">
         <v>30</v>
       </c>
@@ -30341,7 +30348,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="425" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A425" s="1" t="s">
         <v>30</v>
       </c>
@@ -30394,7 +30401,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="426" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A426" s="1" t="s">
         <v>30</v>
       </c>
@@ -30438,7 +30445,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="427" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A427" s="1" t="s">
         <v>30</v>
       </c>
@@ -30491,7 +30498,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="428" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A428" s="1" t="s">
         <v>30</v>
       </c>
@@ -30544,7 +30551,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="429" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A429" s="1" t="s">
         <v>30</v>
       </c>
@@ -30588,7 +30595,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="430" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A430" s="1" t="s">
         <v>30</v>
       </c>
@@ -30632,7 +30639,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="431" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A431" s="1" t="s">
         <v>30</v>
       </c>
@@ -30685,7 +30692,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="432" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A432" s="1" t="s">
         <v>30</v>
       </c>
@@ -30729,7 +30736,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="433" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A433" s="1" t="s">
         <v>30</v>
       </c>
@@ -30782,7 +30789,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="434" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A434" s="1" t="s">
         <v>30</v>
       </c>
@@ -30826,7 +30833,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="435" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A435" s="1" t="s">
         <v>30</v>
       </c>
@@ -30879,7 +30886,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="436" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A436" s="1" t="s">
         <v>30</v>
       </c>
@@ -30923,7 +30930,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="437" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A437" s="1" t="s">
         <v>30</v>
       </c>
@@ -30976,7 +30983,7 @@
         <v>2743</v>
       </c>
     </row>
-    <row r="438" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A438" s="1" t="s">
         <v>30</v>
       </c>
@@ -31029,7 +31036,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="439" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A439" s="1" t="s">
         <v>30</v>
       </c>
@@ -31073,7 +31080,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="440" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A440" s="1" t="s">
         <v>30</v>
       </c>
@@ -31126,7 +31133,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="441" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A441" s="1" t="s">
         <v>30</v>
       </c>
@@ -31179,7 +31186,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="442" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A442" s="1" t="s">
         <v>31</v>
       </c>
@@ -31232,7 +31239,7 @@
         <v>2747</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A443" s="1" t="s">
         <v>31</v>
       </c>
@@ -31285,7 +31292,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="444" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A444" s="1" t="s">
         <v>31</v>
       </c>
@@ -31329,7 +31336,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="445" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A445" s="1" t="s">
         <v>31</v>
       </c>
@@ -31382,7 +31389,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="446" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A446" s="1" t="s">
         <v>31</v>
       </c>
@@ -31426,7 +31433,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="447" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A447" s="1" t="s">
         <v>31</v>
       </c>
@@ -31479,7 +31486,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="448" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A448" s="1" t="s">
         <v>31</v>
       </c>
@@ -31532,7 +31539,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A449" s="1" t="s">
         <v>31</v>
       </c>
@@ -31585,7 +31592,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="450" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A450" s="1" t="s">
         <v>31</v>
       </c>
@@ -31638,7 +31645,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="451" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A451" s="1" t="s">
         <v>31</v>
       </c>
@@ -31682,7 +31689,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="452" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A452" s="1" t="s">
         <v>31</v>
       </c>
@@ -31735,7 +31742,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="453" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A453" s="1" t="s">
         <v>31</v>
       </c>
@@ -31788,7 +31795,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="454" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A454" s="1" t="s">
         <v>31</v>
       </c>
@@ -31832,7 +31839,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="455" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A455" s="1" t="s">
         <v>31</v>
       </c>
@@ -31876,7 +31883,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="456" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A456" s="1" t="s">
         <v>31</v>
       </c>
@@ -31929,7 +31936,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="457" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A457" s="1" t="s">
         <v>31</v>
       </c>
@@ -31982,7 +31989,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="458" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A458" s="1" t="s">
         <v>31</v>
       </c>
@@ -32026,7 +32033,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="459" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A459" s="1" t="s">
         <v>31</v>
       </c>
@@ -32079,7 +32086,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="460" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A460" s="1" t="s">
         <v>31</v>
       </c>
@@ -32123,7 +32130,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="461" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A461" s="1" t="s">
         <v>31</v>
       </c>
@@ -32176,7 +32183,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="462" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A462" s="1" t="s">
         <v>32</v>
       </c>
@@ -32229,7 +32236,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="463" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A463" s="1" t="s">
         <v>32</v>
       </c>
@@ -32282,7 +32289,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="464" spans="1:18" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:18" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A464" s="1" t="s">
         <v>32</v>
       </c>
@@ -32335,7 +32342,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="465" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A465" s="1" t="s">
         <v>32</v>
       </c>
@@ -32379,7 +32386,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="466" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A466" s="1" t="s">
         <v>32</v>
       </c>
@@ -32432,7 +32439,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="467" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A467" s="1" t="s">
         <v>32</v>
       </c>
@@ -32485,7 +32492,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="468" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A468" s="1" t="s">
         <v>32</v>
       </c>
@@ -32538,7 +32545,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="469" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A469" s="1" t="s">
         <v>32</v>
       </c>
@@ -32591,7 +32598,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="470" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A470" s="1" t="s">
         <v>32</v>
       </c>
@@ -32644,7 +32651,7 @@
         <v>2756</v>
       </c>
     </row>
-    <row r="471" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A471" s="1" t="s">
         <v>32</v>
       </c>
@@ -32697,7 +32704,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="472" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A472" s="1" t="s">
         <v>32</v>
       </c>
@@ -32750,7 +32757,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="473" spans="1:18" ht="174.9" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:18" ht="174.9" hidden="1" x14ac:dyDescent="0.4">
       <c r="A473" s="1" t="s">
         <v>32</v>
       </c>
@@ -32803,7 +32810,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="474" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A474" s="1" t="s">
         <v>32</v>
       </c>
@@ -32856,7 +32863,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="475" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A475" s="1" t="s">
         <v>32</v>
       </c>
@@ -32900,7 +32907,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="476" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A476" s="1" t="s">
         <v>32</v>
       </c>
@@ -32944,7 +32951,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="477" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A477" s="1" t="s">
         <v>32</v>
       </c>
@@ -32988,7 +32995,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="478" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A478" s="1" t="s">
         <v>32</v>
       </c>
@@ -33041,7 +33048,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="479" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A479" s="1" t="s">
         <v>32</v>
       </c>
@@ -33085,7 +33092,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="480" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A480" s="1" t="s">
         <v>32</v>
       </c>
@@ -33138,7 +33145,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="481" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A481" s="1" t="s">
         <v>32</v>
       </c>
@@ -33191,7 +33198,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="482" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A482" s="1" t="s">
         <v>33</v>
       </c>
@@ -33235,7 +33242,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="483" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A483" s="1" t="s">
         <v>33</v>
       </c>
@@ -33288,7 +33295,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="484" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A484" s="1" t="s">
         <v>33</v>
       </c>
@@ -33341,7 +33348,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="485" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A485" s="1" t="s">
         <v>33</v>
       </c>
@@ -33394,7 +33401,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="486" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A486" s="1" t="s">
         <v>33</v>
       </c>
@@ -33447,7 +33454,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="487" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A487" s="1" t="s">
         <v>33</v>
       </c>
@@ -33491,7 +33498,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="488" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A488" s="1" t="s">
         <v>33</v>
       </c>
@@ -33544,7 +33551,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="489" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A489" s="1" t="s">
         <v>33</v>
       </c>
@@ -33597,7 +33604,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="490" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A490" s="1" t="s">
         <v>33</v>
       </c>
@@ -33650,7 +33657,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="491" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A491" s="1" t="s">
         <v>33</v>
       </c>
@@ -33694,7 +33701,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="492" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A492" s="1" t="s">
         <v>33</v>
       </c>
@@ -33738,7 +33745,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="493" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A493" s="1" t="s">
         <v>33</v>
       </c>
@@ -33782,7 +33789,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="494" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A494" s="1" t="s">
         <v>33</v>
       </c>
@@ -33826,7 +33833,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="495" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A495" s="1" t="s">
         <v>33</v>
       </c>
@@ -33879,7 +33886,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="496" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A496" s="1" t="s">
         <v>33</v>
       </c>
@@ -33932,7 +33939,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="497" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A497" s="1" t="s">
         <v>33</v>
       </c>
@@ -33985,7 +33992,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="498" spans="1:18" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:18" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A498" s="1" t="s">
         <v>33</v>
       </c>
@@ -34038,7 +34045,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="499" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A499" s="1" t="s">
         <v>33</v>
       </c>
@@ -34091,7 +34098,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="500" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A500" s="1" t="s">
         <v>33</v>
       </c>
@@ -34135,7 +34142,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="501" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A501" s="1" t="s">
         <v>33</v>
       </c>
@@ -34188,7 +34195,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="502" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A502" s="1" t="s">
         <v>34</v>
       </c>
@@ -34241,7 +34248,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="503" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A503" s="1" t="s">
         <v>34</v>
       </c>
@@ -34285,7 +34292,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="504" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A504" s="1" t="s">
         <v>34</v>
       </c>
@@ -34329,7 +34336,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="505" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A505" s="1" t="s">
         <v>34</v>
       </c>
@@ -34373,7 +34380,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="506" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A506" s="1" t="s">
         <v>34</v>
       </c>
@@ -34426,7 +34433,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="507" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A507" s="1" t="s">
         <v>34</v>
       </c>
@@ -34479,7 +34486,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="508" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A508" s="1" t="s">
         <v>34</v>
       </c>
@@ -34523,7 +34530,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="509" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A509" s="1" t="s">
         <v>34</v>
       </c>
@@ -34567,7 +34574,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="510" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A510" s="1" t="s">
         <v>34</v>
       </c>
@@ -34611,7 +34618,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="511" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A511" s="1" t="s">
         <v>34</v>
       </c>
@@ -34664,7 +34671,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="512" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A512" s="1" t="s">
         <v>34</v>
       </c>
@@ -34717,7 +34724,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="513" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A513" s="1" t="s">
         <v>34</v>
       </c>
@@ -34770,7 +34777,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="514" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A514" s="1" t="s">
         <v>34</v>
       </c>
@@ -34823,7 +34830,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="515" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A515" s="1" t="s">
         <v>34</v>
       </c>
@@ -34876,7 +34883,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="516" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A516" s="1" t="s">
         <v>34</v>
       </c>
@@ -34929,7 +34936,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="517" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A517" s="1" t="s">
         <v>34</v>
       </c>
@@ -34973,7 +34980,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="518" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A518" s="1" t="s">
         <v>34</v>
       </c>
@@ -35026,7 +35033,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="519" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A519" s="1" t="s">
         <v>34</v>
       </c>
@@ -35079,7 +35086,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="520" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A520" s="1" t="s">
         <v>34</v>
       </c>
@@ -35132,7 +35139,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="521" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A521" s="1" t="s">
         <v>34</v>
       </c>
@@ -36697,7 +36704,7 @@
         <v>2743</v>
       </c>
       <c r="Q551" s="1" t="s">
-        <v>2750</v>
+        <v>2744</v>
       </c>
       <c r="R551" s="1" t="s">
         <v>2747</v>
@@ -37215,7 +37222,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="562" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A562" s="1" t="s">
         <v>37</v>
       </c>
@@ -37268,7 +37275,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="563" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A563" s="1" t="s">
         <v>37</v>
       </c>
@@ -37321,7 +37328,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="564" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A564" s="1" t="s">
         <v>37</v>
       </c>
@@ -37374,7 +37381,7 @@
         <v>2747</v>
       </c>
     </row>
-    <row r="565" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A565" s="1" t="s">
         <v>37</v>
       </c>
@@ -37427,7 +37434,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="566" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A566" s="1" t="s">
         <v>37</v>
       </c>
@@ -37480,7 +37487,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="567" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A567" s="1" t="s">
         <v>37</v>
       </c>
@@ -37524,7 +37531,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="568" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A568" s="1" t="s">
         <v>37</v>
       </c>
@@ -37577,7 +37584,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="569" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A569" s="1" t="s">
         <v>37</v>
       </c>
@@ -37633,7 +37640,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="570" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A570" s="1" t="s">
         <v>37</v>
       </c>
@@ -37686,7 +37693,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="571" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A571" s="1" t="s">
         <v>37</v>
       </c>
@@ -37739,7 +37746,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="572" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A572" s="1" t="s">
         <v>37</v>
       </c>
@@ -37783,7 +37790,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="573" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A573" s="1" t="s">
         <v>37</v>
       </c>
@@ -37836,7 +37843,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="574" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A574" s="1" t="s">
         <v>37</v>
       </c>
@@ -37889,7 +37896,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="575" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A575" s="1" t="s">
         <v>37</v>
       </c>
@@ -37933,7 +37940,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="576" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A576" s="1" t="s">
         <v>37</v>
       </c>
@@ -37977,7 +37984,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="577" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A577" s="1" t="s">
         <v>37</v>
       </c>
@@ -38030,7 +38037,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="578" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A578" s="1" t="s">
         <v>37</v>
       </c>
@@ -38083,7 +38090,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="579" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A579" s="1" t="s">
         <v>37</v>
       </c>
@@ -38136,7 +38143,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="580" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A580" s="1" t="s">
         <v>37</v>
       </c>
@@ -38189,7 +38196,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="581" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A581" s="1" t="s">
         <v>37</v>
       </c>
@@ -38242,7 +38249,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="582" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A582" s="1" t="s">
         <v>38</v>
       </c>
@@ -38286,7 +38293,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="583" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A583" s="1" t="s">
         <v>38</v>
       </c>
@@ -38339,7 +38346,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="584" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A584" s="1" t="s">
         <v>38</v>
       </c>
@@ -38392,7 +38399,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="585" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A585" s="1" t="s">
         <v>38</v>
       </c>
@@ -38436,7 +38443,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="586" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A586" s="1" t="s">
         <v>38</v>
       </c>
@@ -38489,7 +38496,7 @@
         <v>2756</v>
       </c>
     </row>
-    <row r="587" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A587" s="1" t="s">
         <v>38</v>
       </c>
@@ -38542,7 +38549,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="588" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A588" s="1" t="s">
         <v>38</v>
       </c>
@@ -38595,7 +38602,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="589" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A589" s="1" t="s">
         <v>38</v>
       </c>
@@ -38651,7 +38658,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="590" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A590" s="1" t="s">
         <v>38</v>
       </c>
@@ -38695,7 +38702,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="591" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A591" s="1" t="s">
         <v>38</v>
       </c>
@@ -38739,7 +38746,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="592" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A592" s="1" t="s">
         <v>38</v>
       </c>
@@ -38783,7 +38790,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="593" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A593" s="1" t="s">
         <v>38</v>
       </c>
@@ -38836,7 +38843,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="594" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A594" s="1" t="s">
         <v>38</v>
       </c>
@@ -38889,7 +38896,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="595" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A595" s="1" t="s">
         <v>38</v>
       </c>
@@ -38942,7 +38949,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="596" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A596" s="1" t="s">
         <v>38</v>
       </c>
@@ -38995,7 +39002,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="597" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A597" s="1" t="s">
         <v>38</v>
       </c>
@@ -39048,7 +39055,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="598" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A598" s="1" t="s">
         <v>38</v>
       </c>
@@ -39101,7 +39108,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="599" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A599" s="1" t="s">
         <v>38</v>
       </c>
@@ -39154,7 +39161,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="600" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A600" s="1" t="s">
         <v>38</v>
       </c>
@@ -39207,7 +39214,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="601" spans="1:19" ht="145.75" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:19" ht="145.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A601" s="1" t="s">
         <v>38</v>
       </c>
@@ -39251,7 +39258,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="602" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A602" s="1" t="s">
         <v>39</v>
       </c>
@@ -39304,7 +39311,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="603" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A603" s="1" t="s">
         <v>39</v>
       </c>
@@ -39357,7 +39364,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="604" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A604" s="1" t="s">
         <v>39</v>
       </c>
@@ -39413,7 +39420,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="605" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A605" s="1" t="s">
         <v>39</v>
       </c>
@@ -39466,7 +39473,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="606" spans="1:19" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:19" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A606" s="1" t="s">
         <v>39</v>
       </c>
@@ -39510,7 +39517,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="607" spans="1:19" ht="276.89999999999998" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:19" ht="276.89999999999998" hidden="1" x14ac:dyDescent="0.4">
       <c r="A607" s="1" t="s">
         <v>39</v>
       </c>
@@ -39563,7 +39570,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="608" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A608" s="1" t="s">
         <v>39</v>
       </c>
@@ -39616,7 +39623,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="609" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A609" s="1" t="s">
         <v>39</v>
       </c>
@@ -39660,7 +39667,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="610" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A610" s="1" t="s">
         <v>39</v>
       </c>
@@ -39713,7 +39720,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="611" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A611" s="1" t="s">
         <v>39</v>
       </c>
@@ -39766,7 +39773,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="612" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A612" s="1" t="s">
         <v>39</v>
       </c>
@@ -39819,7 +39826,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="613" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A613" s="1" t="s">
         <v>39</v>
       </c>
@@ -39872,7 +39879,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="614" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A614" s="1" t="s">
         <v>39</v>
       </c>
@@ -39925,7 +39932,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="615" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A615" s="1" t="s">
         <v>39</v>
       </c>
@@ -39978,7 +39985,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="616" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A616" s="1" t="s">
         <v>39</v>
       </c>
@@ -40022,7 +40029,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="617" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A617" s="1" t="s">
         <v>39</v>
       </c>
@@ -40075,7 +40082,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="618" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A618" s="1" t="s">
         <v>39</v>
       </c>
@@ -40119,7 +40126,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="619" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A619" s="1" t="s">
         <v>39</v>
       </c>
@@ -40163,7 +40170,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="620" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A620" s="1" t="s">
         <v>39</v>
       </c>
@@ -40216,7 +40223,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="621" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A621" s="1" t="s">
         <v>39</v>
       </c>
@@ -40269,7 +40276,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="622" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A622" s="1" t="s">
         <v>40</v>
       </c>
@@ -40313,7 +40320,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="623" spans="1:18" ht="160.30000000000001" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:18" ht="160.30000000000001" hidden="1" x14ac:dyDescent="0.4">
       <c r="A623" s="1" t="s">
         <v>40</v>
       </c>
@@ -40357,7 +40364,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="624" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A624" s="1" t="s">
         <v>40</v>
       </c>
@@ -40401,7 +40408,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="625" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A625" s="1" t="s">
         <v>40</v>
       </c>
@@ -40454,7 +40461,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="626" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A626" s="1" t="s">
         <v>40</v>
       </c>
@@ -40498,7 +40505,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="627" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A627" s="1" t="s">
         <v>40</v>
       </c>
@@ -40542,7 +40549,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="628" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A628" s="1" t="s">
         <v>40</v>
       </c>
@@ -40586,7 +40593,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="629" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A629" s="1" t="s">
         <v>40</v>
       </c>
@@ -40630,7 +40637,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="630" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A630" s="1" t="s">
         <v>40</v>
       </c>
@@ -40674,7 +40681,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="631" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A631" s="1" t="s">
         <v>40</v>
       </c>
@@ -40718,7 +40725,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="632" spans="1:18" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:18" ht="409.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A632" s="1" t="s">
         <v>40</v>
       </c>
@@ -40762,7 +40769,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="633" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A633" s="1" t="s">
         <v>40</v>
       </c>
@@ -40806,7 +40813,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="634" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A634" s="1" t="s">
         <v>40</v>
       </c>
@@ -40859,7 +40866,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="635" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A635" s="1" t="s">
         <v>40</v>
       </c>
@@ -40903,7 +40910,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="636" spans="1:18" ht="145.75" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:18" ht="145.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A636" s="1" t="s">
         <v>40</v>
       </c>
@@ -40947,7 +40954,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="637" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A637" s="1" t="s">
         <v>40</v>
       </c>
@@ -40991,7 +40998,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="638" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A638" s="1" t="s">
         <v>40</v>
       </c>
@@ -41035,7 +41042,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="639" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A639" s="1" t="s">
         <v>40</v>
       </c>
@@ -41079,7 +41086,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="640" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A640" s="1" t="s">
         <v>40</v>
       </c>
@@ -41123,7 +41130,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="641" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A641" s="1" t="s">
         <v>40</v>
       </c>
@@ -43185,7 +43192,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="682" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A682" s="1" t="s">
         <v>43</v>
       </c>
@@ -43229,7 +43236,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="683" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A683" s="1" t="s">
         <v>43</v>
       </c>
@@ -43273,7 +43280,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="684" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A684" s="1" t="s">
         <v>43</v>
       </c>
@@ -43317,7 +43324,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="685" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A685" s="1" t="s">
         <v>43</v>
       </c>
@@ -43361,7 +43368,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="686" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A686" s="1" t="s">
         <v>43</v>
       </c>
@@ -43417,7 +43424,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="687" spans="1:19" ht="160.30000000000001" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:19" ht="160.30000000000001" hidden="1" x14ac:dyDescent="0.4">
       <c r="A687" s="1" t="s">
         <v>43</v>
       </c>
@@ -43461,7 +43468,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="688" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A688" s="1" t="s">
         <v>43</v>
       </c>
@@ -43514,7 +43521,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="689" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A689" s="1" t="s">
         <v>43</v>
       </c>
@@ -43567,7 +43574,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="690" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A690" s="1" t="s">
         <v>43</v>
       </c>
@@ -43611,7 +43618,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="691" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A691" s="1" t="s">
         <v>43</v>
       </c>
@@ -43664,7 +43671,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="692" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A692" s="1" t="s">
         <v>43</v>
       </c>
@@ -43717,7 +43724,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="693" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A693" s="1" t="s">
         <v>43</v>
       </c>
@@ -43761,7 +43768,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="694" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A694" s="1" t="s">
         <v>43</v>
       </c>
@@ -43805,7 +43812,7 @@
         <v>2754</v>
       </c>
     </row>
-    <row r="695" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A695" s="1" t="s">
         <v>43</v>
       </c>
@@ -43849,7 +43856,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="696" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A696" s="1" t="s">
         <v>43</v>
       </c>
@@ -43902,7 +43909,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="697" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A697" s="1" t="s">
         <v>43</v>
       </c>
@@ -43955,7 +43962,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="698" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A698" s="1" t="s">
         <v>43</v>
       </c>
@@ -44008,7 +44015,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="699" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A699" s="1" t="s">
         <v>43</v>
       </c>
@@ -44061,7 +44068,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="700" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A700" s="1" t="s">
         <v>43</v>
       </c>
@@ -44117,7 +44124,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="701" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A701" s="1" t="s">
         <v>43</v>
       </c>
@@ -44170,7 +44177,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="702" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A702" s="1" t="s">
         <v>44</v>
       </c>
@@ -44223,7 +44230,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="703" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A703" s="1" t="s">
         <v>44</v>
       </c>
@@ -44276,7 +44283,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="704" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A704" s="1" t="s">
         <v>44</v>
       </c>
@@ -44320,7 +44327,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="705" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A705" s="1" t="s">
         <v>44</v>
       </c>
@@ -44373,7 +44380,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="706" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A706" s="1" t="s">
         <v>44</v>
       </c>
@@ -44426,7 +44433,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="707" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A707" s="1" t="s">
         <v>44</v>
       </c>
@@ -44473,7 +44480,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="708" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A708" s="1" t="s">
         <v>44</v>
       </c>
@@ -44526,7 +44533,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="709" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A709" s="1" t="s">
         <v>44</v>
       </c>
@@ -44570,7 +44577,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="710" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A710" s="1" t="s">
         <v>44</v>
       </c>
@@ -44614,7 +44621,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="711" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A711" s="1" t="s">
         <v>44</v>
       </c>
@@ -44658,7 +44665,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="712" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:19" hidden="1" x14ac:dyDescent="0.4">
       <c r="A712" s="1" t="s">
         <v>44</v>
       </c>
@@ -44711,7 +44718,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="713" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A713" s="1" t="s">
         <v>44</v>
       </c>
@@ -44764,7 +44771,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="714" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A714" s="1" t="s">
         <v>44</v>
       </c>
@@ -44808,7 +44815,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="715" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A715" s="1" t="s">
         <v>44</v>
       </c>
@@ -44861,7 +44868,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="716" spans="1:19" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:19" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A716" s="1" t="s">
         <v>44</v>
       </c>
@@ -44914,7 +44921,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="717" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A717" s="1" t="s">
         <v>44</v>
       </c>
@@ -44967,7 +44974,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="718" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A718" s="1" t="s">
         <v>44</v>
       </c>
@@ -45020,7 +45027,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="719" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A719" s="1" t="s">
         <v>44</v>
       </c>
@@ -45064,7 +45071,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="720" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A720" s="1" t="s">
         <v>44</v>
       </c>
@@ -45117,7 +45124,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="721" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A721" s="1" t="s">
         <v>44</v>
       </c>
@@ -45170,7 +45177,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="722" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A722" s="1" t="s">
         <v>45</v>
       </c>
@@ -45214,7 +45221,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="723" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A723" s="1" t="s">
         <v>45</v>
       </c>
@@ -45267,7 +45274,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="724" spans="1:19" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:19" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A724" s="1" t="s">
         <v>45</v>
       </c>
@@ -45320,7 +45327,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="725" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A725" s="1" t="s">
         <v>45</v>
       </c>
@@ -45373,7 +45380,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="726" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A726" s="1" t="s">
         <v>45</v>
       </c>
@@ -45426,7 +45433,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="727" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A727" s="1" t="s">
         <v>45</v>
       </c>
@@ -45479,7 +45486,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="728" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A728" s="1" t="s">
         <v>45</v>
       </c>
@@ -45532,7 +45539,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="729" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A729" s="1" t="s">
         <v>45</v>
       </c>
@@ -45585,7 +45592,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="730" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A730" s="1" t="s">
         <v>45</v>
       </c>
@@ -45638,7 +45645,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="731" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A731" s="1" t="s">
         <v>45</v>
       </c>
@@ -45679,7 +45686,7 @@
         <v>0</v>
       </c>
       <c r="O731" s="1" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
       <c r="P731" s="1" t="s">
         <v>2739</v>
@@ -45691,7 +45698,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="732" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A732" s="1" t="s">
         <v>45</v>
       </c>
@@ -45747,7 +45754,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="733" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A733" s="1" t="s">
         <v>45</v>
       </c>
@@ -45800,7 +45807,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="734" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A734" s="1" t="s">
         <v>45</v>
       </c>
@@ -45853,7 +45860,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="735" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A735" s="1" t="s">
         <v>45</v>
       </c>
@@ -45906,7 +45913,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="736" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A736" s="1" t="s">
         <v>45</v>
       </c>
@@ -45959,7 +45966,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="737" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A737" s="1" t="s">
         <v>45</v>
       </c>
@@ -46012,7 +46019,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="738" spans="1:18" ht="102" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:18" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A738" s="1" t="s">
         <v>45</v>
       </c>
@@ -46065,7 +46072,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="739" spans="1:18" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:18" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A739" s="1" t="s">
         <v>45</v>
       </c>
@@ -46118,7 +46125,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="740" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A740" s="1" t="s">
         <v>45</v>
       </c>
@@ -46171,7 +46178,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="741" spans="1:18" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:18" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A741" s="1" t="s">
         <v>45</v>
       </c>
@@ -46224,7 +46231,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="742" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A742" s="1" t="s">
         <v>46</v>
       </c>
@@ -46277,7 +46284,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="743" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A743" s="1" t="s">
         <v>46</v>
       </c>
@@ -46321,7 +46328,7 @@
         <v>2764</v>
       </c>
     </row>
-    <row r="744" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A744" s="1" t="s">
         <v>46</v>
       </c>
@@ -46374,7 +46381,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="745" spans="1:18" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:18" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A745" s="1" t="s">
         <v>46</v>
       </c>
@@ -46427,7 +46434,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="746" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A746" s="1" t="s">
         <v>46</v>
       </c>
@@ -46471,7 +46478,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="747" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A747" s="1" t="s">
         <v>46</v>
       </c>
@@ -46515,7 +46522,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="748" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A748" s="1" t="s">
         <v>46</v>
       </c>
@@ -46559,7 +46566,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="749" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A749" s="1" t="s">
         <v>46</v>
       </c>
@@ -46603,7 +46610,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="750" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A750" s="1" t="s">
         <v>46</v>
       </c>
@@ -46656,7 +46663,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="751" spans="1:18" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:18" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A751" s="1" t="s">
         <v>46</v>
       </c>
@@ -46709,7 +46716,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="752" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A752" s="1" t="s">
         <v>46</v>
       </c>
@@ -46750,7 +46757,7 @@
         <v>0</v>
       </c>
       <c r="O752" s="1" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
       <c r="P752" s="1" t="s">
         <v>2739</v>
@@ -46762,7 +46769,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="753" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A753" s="1" t="s">
         <v>46</v>
       </c>
@@ -46806,7 +46813,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="754" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A754" s="1" t="s">
         <v>46</v>
       </c>
@@ -46850,7 +46857,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="755" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A755" s="1" t="s">
         <v>46</v>
       </c>
@@ -46894,7 +46901,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="756" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A756" s="1" t="s">
         <v>46</v>
       </c>
@@ -46938,7 +46945,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="757" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A757" s="1" t="s">
         <v>46</v>
       </c>
@@ -46982,7 +46989,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="758" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A758" s="1" t="s">
         <v>46</v>
       </c>
@@ -47026,7 +47033,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="759" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A759" s="1" t="s">
         <v>46</v>
       </c>
@@ -47079,7 +47086,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="760" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A760" s="1" t="s">
         <v>46</v>
       </c>
@@ -47132,7 +47139,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="761" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A761" s="1" t="s">
         <v>46</v>
       </c>
@@ -49194,7 +49201,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="802" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A802" s="1" t="s">
         <v>49</v>
       </c>
@@ -49247,7 +49254,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="803" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A803" s="1" t="s">
         <v>49</v>
       </c>
@@ -49291,7 +49298,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="804" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A804" s="1" t="s">
         <v>49</v>
       </c>
@@ -49344,7 +49351,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="805" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A805" s="1" t="s">
         <v>49</v>
       </c>
@@ -49388,7 +49395,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="806" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A806" s="1" t="s">
         <v>49</v>
       </c>
@@ -49441,7 +49448,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="807" spans="1:19" ht="409.6" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:19" ht="409.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A807" s="1" t="s">
         <v>49</v>
       </c>
@@ -49494,7 +49501,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="808" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A808" s="1" t="s">
         <v>49</v>
       </c>
@@ -49547,7 +49554,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="809" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A809" s="1" t="s">
         <v>49</v>
       </c>
@@ -49600,7 +49607,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="810" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A810" s="1" t="s">
         <v>49</v>
       </c>
@@ -49653,7 +49660,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="811" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A811" s="1" t="s">
         <v>49</v>
       </c>
@@ -49700,13 +49707,13 @@
         <v>2739</v>
       </c>
       <c r="Q811" s="1" t="s">
-        <v>2750</v>
+        <v>2757</v>
       </c>
       <c r="R811" s="1" t="s">
         <v>2758</v>
       </c>
     </row>
-    <row r="812" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A812" s="1" t="s">
         <v>49</v>
       </c>
@@ -49759,7 +49766,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="813" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A813" s="1" t="s">
         <v>49</v>
       </c>
@@ -49812,7 +49819,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="814" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A814" s="1" t="s">
         <v>49</v>
       </c>
@@ -49856,7 +49863,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="815" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A815" s="1" t="s">
         <v>49</v>
       </c>
@@ -49909,7 +49916,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="816" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A816" s="1" t="s">
         <v>49</v>
       </c>
@@ -49953,7 +49960,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="817" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:19" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A817" s="1" t="s">
         <v>49</v>
       </c>
@@ -49997,7 +50004,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="818" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A818" s="1" t="s">
         <v>49</v>
       </c>
@@ -50050,7 +50057,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="819" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A819" s="1" t="s">
         <v>49</v>
       </c>
@@ -50106,7 +50113,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="820" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A820" s="1" t="s">
         <v>49</v>
       </c>
@@ -50159,7 +50166,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="821" spans="1:19" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:19" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A821" s="1" t="s">
         <v>49</v>
       </c>
@@ -50212,7 +50219,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="822" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A822" s="1" t="s">
         <v>50</v>
       </c>
@@ -50265,7 +50272,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="823" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A823" s="1" t="s">
         <v>50</v>
       </c>
@@ -50318,7 +50325,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="824" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A824" s="1" t="s">
         <v>50</v>
       </c>
@@ -50371,7 +50378,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="825" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A825" s="1" t="s">
         <v>50</v>
       </c>
@@ -50424,7 +50431,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="826" spans="1:19" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:19" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A826" s="1" t="s">
         <v>50</v>
       </c>
@@ -50477,7 +50484,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="827" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A827" s="1" t="s">
         <v>50</v>
       </c>
@@ -50530,7 +50537,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="828" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A828" s="1" t="s">
         <v>50</v>
       </c>
@@ -50583,7 +50590,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="829" spans="1:19" ht="116.6" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:19" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A829" s="1" t="s">
         <v>50</v>
       </c>
@@ -50636,7 +50643,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="830" spans="1:19" ht="102" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A830" s="1" t="s">
         <v>50</v>
       </c>
@@ -50689,7 +50696,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="831" spans="1:19" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="831" spans="1:19" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A831" s="1" t="s">
         <v>50</v>
       </c>
@@ -50742,7 +50749,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="832" spans="1:19" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:19" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A832" s="1" t="s">
         <v>50</v>
       </c>
@@ -50795,7 +50802,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="833" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A833" s="1" t="s">
         <v>50</v>
       </c>
@@ -50848,7 +50855,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="834" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A834" s="1" t="s">
         <v>50</v>
       </c>
@@ -50901,7 +50908,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="835" spans="1:18" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:18" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A835" s="1" t="s">
         <v>50</v>
       </c>
@@ -50954,7 +50961,7 @@
         <v>2747</v>
       </c>
     </row>
-    <row r="836" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A836" s="1" t="s">
         <v>50</v>
       </c>
@@ -51007,7 +51014,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="837" spans="1:18" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:18" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A837" s="1" t="s">
         <v>50</v>
       </c>
@@ -51060,7 +51067,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="838" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A838" s="1" t="s">
         <v>50</v>
       </c>
@@ -51113,7 +51120,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="839" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A839" s="1" t="s">
         <v>50</v>
       </c>
@@ -51166,7 +51173,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="840" spans="1:18" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:18" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A840" s="1" t="s">
         <v>50</v>
       </c>
@@ -51219,7 +51226,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="841" spans="1:18" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:18" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A841" s="1" t="s">
         <v>50</v>
       </c>
@@ -51290,11 +51297,11 @@
     <col min="3" max="3" width="9.61328125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="11.61328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.61328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.3046875" customWidth="1"/>
+    <col min="7" max="7" width="6.23046875" customWidth="1"/>
     <col min="8" max="8" width="4.15234375" customWidth="1"/>
     <col min="9" max="9" width="4.3828125" customWidth="1"/>
     <col min="10" max="10" width="15.3828125" customWidth="1"/>
-    <col min="11" max="11" width="17.765625" customWidth="1"/>
+    <col min="11" max="11" width="17.69140625" customWidth="1"/>
     <col min="12" max="12" width="38" customWidth="1"/>
     <col min="14" max="14" width="13.921875" customWidth="1"/>
     <col min="15" max="15" width="12.61328125" customWidth="1"/>
@@ -51362,7 +51369,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
